--- a/site/suivi_positionnements.xlsx
+++ b/site/suivi_positionnements.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,11 @@
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 — Proposition de script E17 (briefs/antoine_latreille_E17.txt). Ancrage T9 ; frontière E16. Oral : pacte d'associés, sans mention de la loi PACTE. Tournage 24/09 10:30.</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -684,27 +688,65 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>E2 ; E3</t>
+          <t>E3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Joël Nguyen</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Institut d’Optique</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>T2 (E2, E3)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 — Accord potentiel pour la vidéo expert 2 (E2), communiqué oralement. Grégoire Burgé ne fera pas E2.
+2026-09-10 — Script E2 renvoyé (modifications sur la proposition). Se présente : responsable du pôle de développement à la Direction de l’Innovation de l’Institut d’Optique. Texte déposé dans scripts_recus/E2.txt.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Script reçu le 2026-09-10. Revue 1 : resserrement durée (~8 min → ~6 min), frontière E1 (market-pull court) et E3 (s'arrêter à l'hypothèse), coupe exemple SHS et matériau. Proposition dans E2_revue1.json.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Pascal Corbel</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Université Paris-Saclay</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>T9 (E16, E17) ; T10 (E18, E19) ; T11 (E20, E21)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Bonjour Rita-Noeëlle,
 Voici mon retour :
@@ -720,55 +762,31 @@
 Responsable du M2 EMPI
 Université Paris-Saclay
 pascalcorbel.fr
-2026-09-03 — Trois scripts recus (E16, E19, E21) en piece jointe d'un mail a Rita-Noelle Faucon : « Vous trouverez en piece jointe une proposition de script pour les 3 sequences video. N'hesitez pas a faires remarques et a me dire si cela ne correspond pas tout a fait aux attentes. » Remercie pour les informations pratiques. Chaque script est precede d'une ligne de cadrage rappelant la video temoin associee et l'angle retenu (complementarite et apprentissage pour E16 ; deconstruction de la figure de l'entrepreneur visionnaire pour E19 ; essais, erreurs, pivot et leviers pour E21).</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+2026-09-03 — Trois scripts recus (E16, E19, E21) en piece jointe d'un mail a Rita-Noelle Faucon : « Vous trouverez en piece jointe une proposition de script pour les 3 sequences video. N'hesitez pas a faires remarques et a me dire si cela ne correspond pas tout a fait aux attentes. » Remercie pour les informations pratiques. Chaque script est precede d'une ligne de cadrage rappelant la video temoin associee et l'angle retenu (complementarite et apprentissage pour E16 ; deconstruction de la figure de l'entrepreneur visionnaire pour E19 ; essais, erreurs, pivot et leviers pour E21).
+2026-09-07 — Accord sur les inserts : « Je suis d'accord avec vos suggestions de modifications et d'ajouts. » Sur les deux conclusions proches (E19 / E21), precise son raisonnement initial : « j'etais parti du principe que tous les apprenants ne regarderaient pas necessairement toutes les videos, en tout cas avec la meme attention, et que donc il n'etait pas genant de repeter une idee aussi centrale. Ceci etant, pas de probleme pour changer. » Tournage le jour meme a 13h00.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Souhaite un cadrage précis : E16 sur complémentarité et apprentissage ; E18 sur distinction technologie / proposition de valeur ; E19 pour déconstruire la figure de l'entrepreneur visionnaire. Estime qu'un juriste serait plus pertinent pour E17 et ne se juge pas le plus qualifié pour E20.
-2026-09-03 — Demande des remarques et une confirmation d'adequation aux attentes. Points de retour de notre cote : duree en dessous de la cible (E16 2 min 20, E19 2 min 50, E21 3 min 50 pour 5 min +/- 2) ; absence d'ancrage sur les temoignages montes T9/T10/T11 ; recouvrement entre la conclusion de E19 et l'ensemble de E21, avec deux chutes quasi identiques ; presentation de l'intervenant manquante ; coquilles a corriger avant prompteur. Revues annotees E16/E19/E21 et mail unique prets a envoyer.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+2026-09-03 — Demande des remarques et une confirmation d'adequation aux attentes. Points de retour de notre cote : duree en dessous de la cible (E16 2 min 20, E19 2 min 50, E21 3 min 50 pour 5 min +/- 2) ; absence d'ancrage sur les temoignages montes T9/T10/T11 ; recouvrement entre la conclusion de E19 et l'ensemble de E21, avec deux chutes quasi identiques ; presentation de l'intervenant manquante ; coquilles a corriger avant prompteur. Revues annotees E16/E19/E21 et mail unique prets a envoyer. Inserts valides le 07/09/2026 ; scripts arretes pour le tournage du 07/09 (scripts_valides/E16, E19, E21).</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>E19 ; E21</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>E16 ; E19 ; E21</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Rémi Waché</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Université Paris-Saclay</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>T12 (E22, E23)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>E22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Soizic Lefeuvre</t>
+          <t>Rémi Waché</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -778,132 +796,161 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>T4 (E6, E7) ; T5 (E8, E9) ; T6 (E10, E11) ; T12 (E22, E23)</t>
+          <t>T12 (E22, E23)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 — Demande un script déjà rédigé, avec peu de retouches. Proposition déposée (briefs/remi_wache_E22.txt + E22_proposition.json), ~747 mots / 5 min. Ancrage T12 monté (dispositifs, introductions, pitch, cohorte) ; frontière nette avec E23 (Eneli Vino). Tournage 11/09 09:00.</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Stanislas De Lapasse</t>
+          <t>Soizic Lefeuvre</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>INPI</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>T5 (E8, E9)</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Positionnement confirme sur les deux videos proposees (E8 et E9 / T5).</t>
-        </is>
-      </c>
+          <t>T4 (E6, E7) ; T5 (E8, E9) ; T6 (E10, E11) ; T12 (E22, E23)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>E8 ; E9 (acceptation des deux videos proposees)</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>E8 ; E9</t>
+          <t>E11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Stephanie Oger-Roussel</t>
+          <t>Stanislas De Lapasse</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Communication de SATT Paris-Saclay</t>
+          <t>INPI</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>T3 (E4, E5) ; T6 (E10, E11) ; T7 (E12, E13, E13bis) ; T8 (E14, E15)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>T5 (E8, E9)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Positionnement confirme sur les deux videos proposees (E8 et E9 / T5).</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>E8 ; E9 (acceptation des deux videos proposees)</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E8 ; E9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Stephanie Oger-Roussel</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Communication de SATT Paris-Saclay</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>T3 (E4, E5) ; T6 (E10, E11) ; T7 (E12, E13, E13bis) ; T8 (E14, E15)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Stephanie Sano</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>UVSQ (Université de Versailles Saint-Quentin-en-Yvelines)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>T4 (E6, E7)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-07-23 — Positionnement confirme sur les deux videos proposees (E6 et E7 / T4).
 2026-08-31 — Script E6 « Declarer avant de divulguer » envoye pour avis. Question : le script du guide est-il un exemple ou une trame a completer ? Attend un retour avant d ecrire E7.
 2026-08-31 (apres-midi) — Script E7 « A qui parler et avec quoi arriver ? » envoye (titre recu : Charge de valorisation).</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-08-31 — Clarifier le statut du script projete du guide detaille (exemple IA vs trame a completer). Scripts E6 et E7 recus le meme jour ; un seul mail de retour (deux textes annotes en PJ).</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>E6 ; E7 (acceptation des deux videos proposees)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>E6 ; E7</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Virginia Branco</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>ENS Paris-Saclay</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>T3 (E4, E5) ; T6 (E10, E11) ; T12 (E22, E23)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2026-07-22 — Bonjour Rita,
 Je suis en congés du 24/07 au 25/08, le timing est très serré.
@@ -915,42 +962,42 @@
 2026-08-31 — Premier jet scripts E5 et E10 (guide de tournage, ~780 mots chacun). Reformule les témoins dans ses propres mots. Questions : fil conducteur OK ? citation par prénom ? date du tournage ?</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-08-31 — Validation fil conducteur E5/E10 ; confirmation citation chercheurs par prénom ; date de tournage à confirmer.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>E10 ; E11 ; E5 ; E22 (ordre de preference)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>E10 ; E5</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Yoann Montenot</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Université Paris-Saclay</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>T7 (E12, E13, E13bis)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>E13bis</t>
         </is>
@@ -1060,17 +1107,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Gregoire Burgé</t>
+          <t>Joël Nguyen</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>AgroParisTech</t>
+          <t>Institut d’Optique</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Innovation agro / transfert technologique</t>
+          <t>Innovation / accompagnement de projets (Institut d’Optique)</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1808,6 +1855,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1853,40 +1901,45 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Joël Nguyen</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Pascal Corbel</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Rémi Waché</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Soizic Lefeuvre</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Stanislas De Lapasse</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Stephanie Oger-Roussel</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Stephanie Sano</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Virginia Branco</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Yoann Montenot</t>
         </is>
@@ -1922,11 +1975,11 @@
         <v>3</v>
       </c>
       <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K2" s="2" t="n">
         <v>1</v>
       </c>
@@ -1943,6 +1996,9 @@
         <v>1</v>
       </c>
       <c r="P2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1976,11 +2032,11 @@
         <v>4</v>
       </c>
       <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" s="2" t="n">
         <v>1</v>
       </c>
@@ -1997,6 +2053,9 @@
         <v>1</v>
       </c>
       <c r="P3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2030,11 +2089,11 @@
         <v>4</v>
       </c>
       <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" s="2" t="n">
         <v>1</v>
       </c>
@@ -2051,6 +2110,9 @@
         <v>1</v>
       </c>
       <c r="P4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2096,15 +2158,18 @@
         <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2150,15 +2215,18 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2198,21 +2266,24 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>5</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2249,24 +2320,27 @@
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N8" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="O8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2306,21 +2380,24 @@
         <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L9" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="M9" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2357,10 +2434,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>5</v>
@@ -2375,6 +2452,9 @@
         <v>5</v>
       </c>
       <c r="P10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2411,24 +2491,27 @@
         <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2465,24 +2548,27 @@
         <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="L12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="N12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="N12" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="O12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2528,15 +2614,18 @@
         <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2570,11 +2659,11 @@
         <v>5</v>
       </c>
       <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K14" s="2" t="n">
         <v>1</v>
       </c>
@@ -2591,6 +2680,9 @@
         <v>1</v>
       </c>
       <c r="P14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2624,10 +2716,10 @@
         <v>4</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>1</v>
@@ -2645,6 +2737,9 @@
         <v>1</v>
       </c>
       <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2690,15 +2785,18 @@
         <v>1</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2735,13 +2833,13 @@
         <v>1</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
@@ -2753,6 +2851,9 @@
         <v>1</v>
       </c>
       <c r="P17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2786,13 +2887,13 @@
         <v>1</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>1</v>
@@ -2807,6 +2908,9 @@
         <v>1</v>
       </c>
       <c r="P18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2843,24 +2947,27 @@
         <v>1</v>
       </c>
       <c r="J19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2894,27 +3001,30 @@
         <v>1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L20" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2948,10 +3058,10 @@
         <v>2</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>1</v>
@@ -2969,6 +3079,9 @@
         <v>1</v>
       </c>
       <c r="P21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3005,13 +3118,13 @@
         <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -3023,6 +3136,9 @@
         <v>1</v>
       </c>
       <c r="P22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3056,11 +3172,11 @@
         <v>1</v>
       </c>
       <c r="I23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K23" s="2" t="n">
         <v>1</v>
       </c>
@@ -3077,6 +3193,9 @@
         <v>1</v>
       </c>
       <c r="P23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3110,27 +3229,30 @@
         <v>1</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3167,7 +3289,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>5</v>
@@ -3176,15 +3298,18 @@
         <v>5</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O25" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="P25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="2" t="n">
         <v>1</v>
       </c>
     </row>

--- a/site/suivi_positionnements.xlsx
+++ b/site/suivi_positionnements.xlsx
@@ -799,10 +799,15 @@
           <t>T12 (E22, E23)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 — Script revu/corrigé reçu (voix cellule partenariats UPS : point d’entrée, prospection, collaboration vs prestation, NDA, dimensionnement, négociation, six repères, chute public-privé). Déposé scripts_recus/E22.txt ; prompteur scripts_valides/E22.txt (coquilles seulement).</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 — Demande un script déjà rédigé, avec peu de retouches. Proposition déposée (briefs/remi_wache_E22.txt + E22_proposition.json), ~747 mots / 5 min. Ancrage T12 monté (dispositifs, introductions, pitch, cohorte) ; frontière nette avec E23 (Eneli Vino). Tournage 11/09 09:00.</t>
+          <t>2026-09-08 — Demande un script déjà rédigé, avec peu de retouches. Proposition déposée (briefs/remi_wache_E22.txt + E22_proposition.json).
+2026-09-11 — Version Rémi arrêtée pour tournage (~1200 mots / ~8 min). Recouvrement E23 conservé (renvoi à la vidéo suivante).</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>

--- a/site/suivi_positionnements.xlsx
+++ b/site/suivi_positionnements.xlsx
@@ -498,7 +498,8 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 — Proposition de script E17 (briefs/antoine_latreille_E17.txt). Ancrage T9 ; frontière E16. Oral : pacte d'associés, sans mention de la loi PACTE. Tournage 24/09 10:30.</t>
+          <t>2026-09-10 — Proposition de script E17 (briefs/antoine_latreille_E17.txt). Ancrage T9 ; frontière E16. Oral : pacte d'associés, sans mention de la loi PACTE.
+2026-09-24 — Filmé E17 (10:30, IncubAlliance). V0 pas encore importé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -525,7 +526,11 @@
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 — Filmé E13, E15, E18 (09:00, IncubAlliance). V0 pas encore importé.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -612,7 +617,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>T3 (E4, E5) ; T6 (E10, E11) ; T7 (E12, E13, E13bis) ; T8 (E14, E15) ; T12 (E22, E23)</t>
+          <t>T3 (E4, E5) ; T6 (E10, E11, E11bis) ; T7 (E12, E13, E13bis) ; T8 (E14, E15) ; T12 (E22, E23)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -635,7 +640,8 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Demande la transmission des capsules témoins T3, T7 et T8. Souhaite commenter plus précisément les scripts après retour sur le positionnement retenu. Absente jusqu'au 14 août inclus.</t>
+          <t>Demande la transmission des capsules témoins T3, T7 et T8. Souhaite commenter plus précisément les scripts après retour sur le positionnement retenu. Absente jusqu'au 14 août inclus.
+2026-09-24 — E12 repris par Stephanie Oger-Roussel (texte SATT). E4 (niveaux de preuve, T3) proposé à Fatoumata ; E14 conservé. Si refus : recaster E4 (Joël, Bernard, Grégoire — dans cet ordre). Accord Fatoumata à obtenir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -645,7 +651,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>E12 ; E14</t>
+          <t>E4 ; E14</t>
         </is>
       </c>
     </row>
@@ -678,7 +684,8 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Point à la rentrée pour clarifier le lien script / sujets expert et cadrer l'intervention. Préfère parler sans script pré-écrit.</t>
+          <t>Point à la rentrée pour clarifier le lien script / sujets expert et cadrer l'intervention. Préfère parler sans script pré-écrit.
+2026-09-24 — Filmé E3 (14:30, IncubAlliance). V0 pas encore importé.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -716,7 +723,8 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Script reçu le 2026-09-10. Revue 1 : resserrement durée (~8 min → ~6 min), frontière E1 (market-pull court) et E3 (s'arrêter à l'hypothèse), coupe exemple SHS et matériau. Proposition dans E2_revue1.json.</t>
+          <t>Script reçu le 2026-09-10. Revue 1 : resserrement durée (~8 min → ~6 min), frontière E1 (market-pull court) et E3 (s'arrêter à l'hypothèse), coupe exemple SHS et matériau. Proposition dans E2_revue1.json.
+2026-09-24 — Non filmé (créneau 16:00 à confirmer, non cité parmi les tournages du jour). À reprogrammer.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -830,15 +838,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>T4 (E6, E7) ; T5 (E8, E9) ; T6 (E10, E11) ; T12 (E22, E23)</t>
+          <t>T4 (E6, E7) ; T5 (E8, E9) ; T6 (E10, E11, E11bis) ; T12 (E22, E23)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 — E11bis optionnelle : loi PACTE / Allègre, concours scientifique. Grain T6 (statut de l'agent au moment du choix de voie), pas T8 (financements). Distincte de E11 (contrats) et de E17 (pacte d'associés). Accord et créneau à obtenir.</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E11 ; E11bis (optionnel)</t>
         </is>
       </c>
     </row>
@@ -888,15 +900,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>T3 (E4, E5) ; T6 (E10, E11) ; T7 (E12, E13, E13bis) ; T8 (E14, E15)</t>
+          <t>T3 (E4, E5) ; T6 (E10, E11, E11bis) ; T7 (E12, E13, E13bis) ; T8 (E14, E15)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 — Swap : son script SATT devient E12. Filmé E12 (12:00, IncubAlliance). V0 pas encore importé. E4 proposé à Fatoumata.</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E12</t>
         </is>
       </c>
     </row>
@@ -952,7 +968,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>T3 (E4, E5) ; T6 (E10, E11) ; T12 (E22, E23)</t>
+          <t>T3 (E4, E5) ; T6 (E10, E11, E11bis) ; T12 (E22, E23)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1019,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1176,17 +1192,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Stephanie Oger-Roussel</t>
+          <t>Fatoumata Aonon</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Communication de SATT Paris-Saclay</t>
+          <t>CNRS</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Stratégie innovation / transfert (SATT Paris-Saclay)</t>
+          <t>Valorisation recherche / accompagnement projets</t>
         </is>
       </c>
     </row>
@@ -1417,214 +1433,214 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E11BIS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 12</t>
+          <t>Vidéo Expert 11 BIS</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Étapes, sélection, investissement, jalons et accompagnement.</t>
+          <t>Optionnel. Regime de l'agent public (loi Allegre 1999 / loi PACTE 2019) : participer a une societe qui valorise ses travaux sans quitter l'etablissement. Temps de service, parts, fonctions. Ce n'est pas un concours de financement (i-Lab). Distinct du pacte d'associes (E17).</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Fatoumata Aonon</t>
+          <t>Soizic Lefeuvre</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CNRS</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Valorisation recherche / accompagnement projets</t>
+          <t>Partenariat et valorisation / droit contrats et PI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 13</t>
+          <t>Vidéo Expert 12</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Coaching, réseau, formation, confrontation, équipe et préparation de la création.</t>
+          <t>Étapes, sélection, investissement, jalons et accompagnement.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé</t>
+          <t>Stephanie Oger-Roussel</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>IncubAlliance</t>
+          <t>Communication de SATT Paris-Saclay</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneuriat deeptech / incubation</t>
+          <t>Stratégie innovation / transfert (SATT Paris-Saclay)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>E13BIS</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 13 BIS</t>
+          <t>Vidéo Expert 13</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Design spot, fablab, pole de competitivite, OTT, etc. — pour les start-up de nos chercheurs, pas des start-up generiques.</t>
+          <t>Coaching, réseau, formation, confrontation, équipe et préparation de la création.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Yoann Montenot</t>
+          <t>Arielle Santé</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Université Paris-Saclay</t>
+          <t>IncubAlliance</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Design d'innovation / Design Spot Paris-Saclay</t>
+          <t>Entrepreneuriat deeptech / incubation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E13BIS</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 14</t>
+          <t>Vidéo Expert 13 BIS</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Prématuration, maturation, aides non dilutives, concours, Bpifrance et financement prive.</t>
+          <t>Design spot, fablab, pole de competitivite, OTT, etc. — pour les start-up de nos chercheurs, pas des start-up generiques.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fatoumata Aonon</t>
+          <t>Yoann Montenot</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CNRS</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Valorisation recherche / accompagnement projets</t>
+          <t>Design d'innovation / Design Spot Paris-Saclay</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 15</t>
+          <t>Vidéo Expert 14</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Dilution, retour attendu, rythme de croissance, gouvernance et compatibilite avec le projet.</t>
+          <t>Prématuration, maturation, aides non dilutives, concours, Bpifrance et financement prive.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé</t>
+          <t>Fatoumata Aonon</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>IncubAlliance</t>
+          <t>CNRS</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneuriat deeptech / incubation</t>
+          <t>Valorisation recherche / accompagnement projets</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 16</t>
+          <t>Vidéo Expert 15</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Complémentarité, recrutement, rôle du CEO, du CSO et du CTO, et criteres humains.</t>
+          <t>Dilution, retour attendu, rythme de croissance, gouvernance et compatibilite avec le projet.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Pascal Corbel</t>
+          <t>Arielle Santé</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Université Paris-Saclay</t>
+          <t>IncubAlliance</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Management innovation / PI / entrepreneuriat</t>
+          <t>Entrepreneuriat deeptech / incubation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 17</t>
+          <t>Vidéo Expert 16</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Gouvernance, responsabilites, repartition du pouvoir, parts, pacte et prevention des conflits.</t>
+          <t>Complémentarité, recrutement, rôle du CEO, du CSO et du CTO, et criteres humains.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Antoine Latreille</t>
+          <t>Pascal Corbel</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1634,157 +1650,157 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Droit de l'innovation / propriété industrielle</t>
+          <t>Management innovation / PI / entrepreneuriat</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 18</t>
+          <t>Vidéo Expert 17</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Adapter le message selon l'utilisateur, le decideur, le partenaire ou l'investisseur.</t>
+          <t>Gouvernance, responsabilites, repartition du pouvoir, parts, pacte et prevention des conflits.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé</t>
+          <t>Antoine Latreille</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>IncubAlliance</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneuriat deeptech / incubation</t>
+          <t>Droit de l'innovation / propriété industrielle</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 19</t>
+          <t>Vidéo Expert 18</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Feedback, entrainement, mentorat et evolution de l'identite professionnelle.</t>
+          <t>Adapter le message selon l'utilisateur, le decideur, le partenaire ou l'investisseur.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Pascal Corbel</t>
+          <t>Arielle Santé</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Université Paris-Saclay</t>
+          <t>IncubAlliance</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Management innovation / PI / entrepreneuriat</t>
+          <t>Entrepreneuriat deeptech / incubation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 20</t>
+          <t>Vidéo Expert 19</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Double casquette, gouvernance, impartialite, evolution du metier de chercheur.</t>
+          <t>Feedback, entrainement, mentorat et evolution de l'identite professionnelle.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Bernard Yannou</t>
+          <t>Pascal Corbel</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CentraleSupélec</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Innovation / design engineering / deeptech</t>
+          <t>Management innovation / PI / entrepreneuriat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 21</t>
+          <t>Vidéo Expert 20</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Incertitude, essais, erreurs, pivot et progression plutot que reussite lineaire ; leviers existants pour depasser les freins.</t>
+          <t>Double casquette, gouvernance, impartialite, evolution du metier de chercheur.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Pascal Corbel</t>
+          <t>Bernard Yannou</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Université Paris-Saclay</t>
+          <t>CentraleSupélec</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Management innovation / PI / entrepreneuriat</t>
+          <t>Innovation / design engineering / deeptech</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 22</t>
+          <t>Vidéo Expert 21</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Objectifs partages, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+          <t>Incertitude, essais, erreurs, pivot et progression plutot que reussite lineaire ; leviers existants pour depasser les freins.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Rémi Waché</t>
+          <t>Pascal Corbel</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1794,37 +1810,69 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Développement de partenariats recherche-industrie</t>
+          <t>Management innovation / PI / entrepreneuriat</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vidéo Expert 22</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Objectifs partages, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Rémi Waché</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Université Paris-Saclay</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Développement de partenariats recherche-industrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>E23</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Vidéo Expert 23</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Confidentialite, contrats, connaissances anterieures, résultats nouveaux, PI, publication et sortie du partenariat.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Eneli Vino</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>CNRS</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Juridique PI / contrats / valorisation</t>
         </is>
@@ -1841,7 +1889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2580,19 +2628,19 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 12</t>
+          <t>Vidéo Expert 11 BIS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Étapes, sélection, investissement, jalons et accompagnement.</t>
+          <t>Optionnel. Regime de l'agent public (loi Allegre 1999 / loi PACTE 2019) : participer a une societe qui valorise ses travaux sans quitter l'etablissement. Temps de service, parts, fonctions. Ce n'est pas un concours de financement (i-Lab). Distinct du pacte d'associes (E17).</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
@@ -2601,10 +2649,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -2622,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
@@ -2631,18 +2679,18 @@
         <v>1</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 13</t>
+          <t>Vidéo Expert 12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Coaching, réseau, formation, confrontation, équipe et préparation de la création.</t>
+          <t>Étapes, sélection, investissement, jalons et accompagnement.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -2658,48 +2706,48 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 13 BIS</t>
+          <t>Vidéo Expert 13</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Design spot, fablab, pole de competitivite, OTT, etc. — pour les start-up de nos chercheurs, pas des start-up generiques.</t>
+          <t>Coaching, réseau, formation, confrontation, équipe et préparation de la création.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -2709,79 +2757,79 @@
         <v>5</v>
       </c>
       <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="n">
+      <c r="K15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 14</t>
+          <t>Vidéo Expert 13 BIS</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Prématuration, maturation, aides non dilutives, concours, Bpifrance et financement prive.</t>
+          <t>Design spot, fablab, pole de competitivite, OTT, etc. — pour les start-up de nos chercheurs, pas des start-up generiques.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1</v>
@@ -2793,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>1</v>
@@ -2802,34 +2850,34 @@
         <v>1</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 15</t>
+          <t>Vidéo Expert 14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Dilution, retour attendu, rythme de croissance, gouvernance et compatibilite avec le projet.</t>
+          <t>Prématuration, maturation, aides non dilutives, concours, Bpifrance et financement prive.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1</v>
@@ -2841,16 +2889,16 @@
         <v>1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="2" t="n">
         <v>1</v>
@@ -2865,12 +2913,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 16</t>
+          <t>Vidéo Expert 15</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Complémentarité, recrutement, rôle du CEO, du CSO et du CTO, et criteres humains.</t>
+          <t>Dilution, retour attendu, rythme de croissance, gouvernance et compatibilite avec le projet.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -2883,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>1</v>
@@ -2895,13 +2943,13 @@
         <v>1</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
@@ -2922,25 +2970,25 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 17</t>
+          <t>Vidéo Expert 16</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Gouvernance, responsabilites, repartition du pouvoir, parts, pacte et prevention des conflits.</t>
+          <t>Complémentarité, recrutement, rôle du CEO, du CSO et du CTO, et criteres humains.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1</v>
@@ -2952,25 +3000,25 @@
         <v>1</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>1</v>
@@ -2979,52 +3027,52 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 18</t>
+          <t>Vidéo Expert 17</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Adapter le message selon l'utilisateur, le decideur, le partenaire ou l'investisseur.</t>
+          <t>Gouvernance, responsabilites, repartition du pouvoir, parts, pacte et prevention des conflits.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>3</v>
@@ -3036,16 +3084,16 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 19</t>
+          <t>Vidéo Expert 18</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Feedback, entrainement, mentorat et evolution de l'identite professionnelle.</t>
+          <t>Adapter le message selon l'utilisateur, le decideur, le partenaire ou l'investisseur.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>5</v>
@@ -3054,37 +3102,37 @@
         <v>3</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>1</v>
@@ -3093,43 +3141,43 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 20</t>
+          <t>Vidéo Expert 19</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Double casquette, gouvernance, impartialite, evolution du metier de chercheur.</t>
+          <t>Feedback, entrainement, mentorat et evolution de l'identite professionnelle.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -3150,25 +3198,25 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 21</t>
+          <t>Vidéo Expert 20</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Incertitude, essais, erreurs, pivot et progression plutot que reussite lineaire ; leviers existants pour depasser les freins.</t>
+          <t>Double casquette, gouvernance, impartialite, evolution du metier de chercheur.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1</v>
@@ -3180,13 +3228,13 @@
         <v>1</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -3207,55 +3255,55 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 22</t>
+          <t>Vidéo Expert 21</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Objectifs partages, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+          <t>Incertitude, essais, erreurs, pivot et progression plutot que reussite lineaire ; leviers existants pour depasser les freins.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="K24" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>1</v>
@@ -3264,57 +3312,114 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>Vidéo Expert 22</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Objectifs partages, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Vidéo Expert 23</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Confidentialite, contrats, connaissances anterieures, résultats nouveaux, PI, publication et sortie du partenariat.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="2" t="n">
+      <c r="C26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" s="2" t="n">
+      <c r="H26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q25" s="2" t="n">
+      <c r="P26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="2" t="n">
         <v>1</v>
       </c>
     </row>

--- a/site/suivi_positionnements.xlsx
+++ b/site/suivi_positionnements.xlsx
@@ -499,7 +499,8 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-09-10 — Proposition de script E17 (briefs/antoine_latreille_E17.txt). Ancrage T9 ; frontière E16. Oral : pacte d'associés, sans mention de la loi PACTE.
-2026-09-24 — Filmé E17 (10:30, IncubAlliance). V0 pas encore importé.</t>
+2026-09-24 — Filmé E17 (10:30, IncubAlliance).
+2026-09-25 — Script final = texte fourni par Antoine (scripts_recus/E17.txt, scripts_valides/E17.txt). Éléments de langage PI (FTO, NDA, etc.) exclus du script final.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -528,7 +529,8 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 — Filmé E13, E15, E18 (09:00, IncubAlliance). V0 pas encore importé.</t>
+          <t>2026-09-24 — Filmé E13, E15, E18 (09:00, IncubAlliance). V0 pas encore importé.
+2026-09-25 — Scripts finaux = textes fournis par Arielle (recus + valides E13, E15, E18), déposés tels quels.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -685,7 +687,8 @@
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Point à la rentrée pour clarifier le lien script / sujets expert et cadrer l'intervention. Préfère parler sans script pré-écrit.
-2026-09-24 — Filmé E3 (14:30, IncubAlliance). V0 pas encore importé.</t>
+2026-09-24 — Filmé E3 (14:30, IncubAlliance). V0 pas encore importé.
+2026-09-25 — Script final = texte fourni par Grégoire (scripts_recus/E3.txt, scripts_valides/E3.txt). Texte tel quel, sans réécriture. Techno-push / market-pull : contraste pour renforcer le market-pull, pas une leçon d'origines (E1). Frontière E2 à recadrer ensuite côté Joël (pas encore tourné).</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">

--- a/site/suivi_positionnements.xlsx
+++ b/site/suivi_positionnements.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Suivi positionnements" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Selection finale" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Matrice coherence" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suivi positionnements" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection finale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrice coherence" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,7 +643,9 @@
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Demande la transmission des capsules témoins T3, T7 et T8. Souhaite commenter plus précisément les scripts après retour sur le positionnement retenu. Absente jusqu'au 14 août inclus.
-2026-09-24 — E12 repris par Stephanie Oger-Roussel (texte SATT). E4 (niveaux de preuve, T3) proposé à Fatoumata ; E14 conservé. Si refus : recaster E4 (Joël, Bernard, Grégoire — dans cet ordre). Accord Fatoumata à obtenir.</t>
+2026-09-24 — E12 repris par Stephanie Oger-Roussel (texte SATT). E4 (niveaux de preuve, T3) proposé à Fatoumata ; E14 conservé. Si refus : recaster E4 (Joël, Bernard, Grégoire — dans cet ordre). Accord Fatoumata à obtenir.
+2026-10-14 — CoPil INNO (dit à Juliette Guérin) : E14 envisagée avec le CNRS ; E4 (TRL, DRL, niveaux de preuve) envisagée avec Célia Galkowski (INRAE). Accords à confirmer.
+2026-10-21 — Fatoumata reprend E4 et E14. Guide simplifié avec deux scripts proposés, sans transcript des vidéos témoins (briefs/guide_simplifie_fatoumata_E4_E14.doc). Les vidéos témoins lui sont envoyées à part.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -721,7 +723,10 @@
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-09-08 — Accord potentiel pour la vidéo expert 2 (E2), communiqué oralement. Grégoire Burgé ne fera pas E2.
-2026-09-10 — Script E2 renvoyé (modifications sur la proposition). Se présente : responsable du pôle de développement à la Direction de l’Innovation de l’Institut d’Optique. Texte déposé dans scripts_recus/E2.txt.</t>
+2026-09-10 — Script E2 renvoyé (modifications sur la proposition). Se présente : responsable du pôle de développement à la Direction de l’Innovation de l’Institut d’Optique. Texte déposé dans scripts_recus/E2.txt.
+2026-10-16 — Reprend le script avant captation du 30 octobre. Demande la place exacte dans le parcours, les raccords témoins indispensables, la durée cible, les scripts voisins. Intention : techno-push / market-pull moins binaire ; rencontre entre ce que la techno rend possible et un problème, des usages, des acteurs, un marché.
+2026-10-16 — Réponse Christophe envoyée : lien proto https://tyrulfr.github.io/Oser-Pour-Innover-SCORM/ ; parler après T2 et avant Grégoire (libellé « Market Pull » dans le mail).
+2026-10-16 — Mail de précision : script = trame IA / exemple ; pas binaire ; complémentarité avec Grégoire (même objectif : recherche → innovation).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
